--- a/5. 월별 적용 LNG 단가_2022년부터.xlsx
+++ b/5. 월별 적용 LNG 단가_2022년부터.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\업무\0. 업무 (2026년)\전력시장 일일실적 분석\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F71E189-424B-4576-AB45-87FF4062149E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98339662-8CE4-430F-9D1A-3DEC1499D548}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -223,9 +223,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="176" fontId="5" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -245,6 +242,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="5" fillId="3" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -579,7 +579,7 @@
       </c>
     </row>
     <row r="8" spans="10:23" x14ac:dyDescent="0.2">
-      <c r="J8" s="6">
+      <c r="J8" s="13">
         <v>2026</v>
       </c>
       <c r="K8" s="5" t="s">
@@ -635,7 +635,9 @@
       </c>
     </row>
     <row r="9" spans="10:23" x14ac:dyDescent="0.2">
-      <c r="J9" s="6"/>
+      <c r="J9" s="13">
+        <v>2026</v>
+      </c>
       <c r="K9" s="5" t="s">
         <v>1</v>
       </c>
@@ -689,7 +691,9 @@
       </c>
     </row>
     <row r="10" spans="10:23" x14ac:dyDescent="0.2">
-      <c r="J10" s="6"/>
+      <c r="J10" s="13">
+        <v>2026</v>
+      </c>
       <c r="K10" s="5" t="s">
         <v>2</v>
       </c>
@@ -743,7 +747,7 @@
       </c>
     </row>
     <row r="11" spans="10:23" x14ac:dyDescent="0.2">
-      <c r="J11" s="6">
+      <c r="J11" s="13">
         <v>2025</v>
       </c>
       <c r="K11" s="5" t="s">
@@ -799,7 +803,9 @@
       </c>
     </row>
     <row r="12" spans="10:23" x14ac:dyDescent="0.2">
-      <c r="J12" s="6"/>
+      <c r="J12" s="13">
+        <v>2025</v>
+      </c>
       <c r="K12" s="5" t="s">
         <v>1</v>
       </c>
@@ -853,7 +859,9 @@
       </c>
     </row>
     <row r="13" spans="10:23" x14ac:dyDescent="0.2">
-      <c r="J13" s="6"/>
+      <c r="J13" s="13">
+        <v>2025</v>
+      </c>
       <c r="K13" s="5" t="s">
         <v>2</v>
       </c>
@@ -907,7 +915,7 @@
       </c>
     </row>
     <row r="14" spans="10:23" x14ac:dyDescent="0.2">
-      <c r="J14" s="6">
+      <c r="J14" s="13">
         <v>2024</v>
       </c>
       <c r="K14" s="5" t="s">
@@ -963,7 +971,9 @@
       </c>
     </row>
     <row r="15" spans="10:23" x14ac:dyDescent="0.2">
-      <c r="J15" s="6"/>
+      <c r="J15" s="13">
+        <v>2024</v>
+      </c>
       <c r="K15" s="5" t="s">
         <v>1</v>
       </c>
@@ -1017,7 +1027,9 @@
       </c>
     </row>
     <row r="16" spans="10:23" ht="14.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="J16" s="6"/>
+      <c r="J16" s="13">
+        <v>2024</v>
+      </c>
       <c r="K16" s="5" t="s">
         <v>2</v>
       </c>
@@ -1071,341 +1083,342 @@
       </c>
     </row>
     <row r="17" spans="10:23" x14ac:dyDescent="0.2">
-      <c r="J17" s="6">
+      <c r="J17" s="13">
         <v>2023</v>
       </c>
       <c r="K17" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="L17" s="7">
+      <c r="L17" s="6">
         <f>GJ당!D16*(4.1868*10.19)/10^3</f>
         <v>1495.8276794564399</v>
       </c>
-      <c r="M17" s="7">
+      <c r="M17" s="6">
         <f>GJ당!E16*(4.1868*10.19)/10^3</f>
         <v>1477.57410440424</v>
       </c>
-      <c r="N17" s="7">
+      <c r="N17" s="6">
         <f>GJ당!F16*(4.1868*10.19)/10^3</f>
         <v>1390.92071243796</v>
       </c>
-      <c r="O17" s="8">
+      <c r="O17" s="7">
         <f>GJ당!G16*(4.1868*10.19)/10^3</f>
         <v>1007.3008316120399</v>
       </c>
-      <c r="P17" s="8">
+      <c r="P17" s="7">
         <f>GJ당!H16*(4.1868*10.19)/10^3</f>
         <v>915.42201514559997</v>
       </c>
-      <c r="Q17" s="9">
+      <c r="Q17" s="8">
         <f>GJ당!I16*(4.1868*10.19)/10^3</f>
         <v>881.11075497444006</v>
       </c>
-      <c r="R17" s="7">
+      <c r="R17" s="6">
         <f>GJ당!J16*(4.1868*10.19)/10^3</f>
         <v>914.40705067091994</v>
       </c>
-      <c r="S17" s="7">
+      <c r="S17" s="6">
         <f>GJ당!K16*(4.1868*10.19)/10^3</f>
         <v>860.99747830595993</v>
       </c>
-      <c r="T17" s="7">
+      <c r="T17" s="6">
         <f>GJ당!L16*(4.1868*10.19)/10^3</f>
         <v>849.24453952980002</v>
       </c>
-      <c r="U17" s="10">
+      <c r="U17" s="9">
         <f>GJ당!M16*(4.1868*10.19)/10^3</f>
         <v>902.64984554555997</v>
       </c>
-      <c r="V17" s="7">
+      <c r="V17" s="6">
         <f>GJ당!N16*(4.1868*10.19)/10^3</f>
         <v>804.56647743756002</v>
       </c>
-      <c r="W17" s="7">
+      <c r="W17" s="6">
         <f>GJ당!O16*(4.1868*10.19)/10^3</f>
         <v>861.73811652708002</v>
       </c>
     </row>
     <row r="18" spans="10:23" x14ac:dyDescent="0.2">
-      <c r="J18" s="6"/>
+      <c r="J18" s="13">
+        <v>2023</v>
+      </c>
       <c r="K18" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="L18" s="10">
+      <c r="L18" s="9">
         <f>GJ당!D17*(4.1868*10.19)/10^3</f>
         <v>44.527459965479999</v>
       </c>
-      <c r="M18" s="10">
+      <c r="M18" s="9">
         <f>GJ당!E17*(4.1868*10.19)/10^3</f>
         <v>44.527459965479999</v>
       </c>
-      <c r="N18" s="10">
+      <c r="N18" s="9">
         <f>GJ당!F17*(4.1868*10.19)/10^3</f>
         <v>44.527459965479999</v>
       </c>
-      <c r="O18" s="10">
+      <c r="O18" s="9">
         <f>GJ당!G17*(4.1868*10.19)/10^3</f>
         <v>44.527459965479999</v>
       </c>
-      <c r="P18" s="11">
+      <c r="P18" s="10">
         <f>GJ당!H17*(4.1868*10.19)/10^3</f>
         <v>61.219124575560002</v>
       </c>
-      <c r="Q18" s="11">
+      <c r="Q18" s="10">
         <f>GJ당!I17*(4.1868*10.19)/10^3</f>
         <v>61.219124575560002</v>
       </c>
-      <c r="R18" s="11">
+      <c r="R18" s="10">
         <f>GJ당!J17*(4.1868*10.19)/10^3</f>
         <v>61.219124575560002</v>
       </c>
-      <c r="S18" s="11">
+      <c r="S18" s="10">
         <f>GJ당!K17*(4.1868*10.19)/10^3</f>
         <v>61.219124575560002</v>
       </c>
-      <c r="T18" s="10">
+      <c r="T18" s="9">
         <f>GJ당!L17*(4.1868*10.19)/10^3</f>
         <v>61.219124575560002</v>
       </c>
-      <c r="U18" s="12">
+      <c r="U18" s="11">
         <f>GJ당!M17*(4.1868*10.19)/10^3</f>
         <v>61.219124575560002</v>
       </c>
-      <c r="V18" s="10">
+      <c r="V18" s="9">
         <f>GJ당!N17*(4.1868*10.19)/10^3</f>
         <v>61.219124575560002</v>
       </c>
-      <c r="W18" s="10">
+      <c r="W18" s="9">
         <f>GJ당!O17*(4.1868*10.19)/10^3</f>
         <v>61.219124575560002</v>
       </c>
     </row>
     <row r="19" spans="10:23" ht="14.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="J19" s="6"/>
+      <c r="J19" s="13">
+        <v>2023</v>
+      </c>
       <c r="K19" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="L19" s="13">
+      <c r="L19" s="12">
         <f>GJ당!D18*(4.1868*10.19)/10^3</f>
         <v>1540.3551394219201</v>
       </c>
-      <c r="M19" s="13">
+      <c r="M19" s="12">
         <f>GJ당!E18*(4.1868*10.19)/10^3</f>
         <v>1522.1015643697201</v>
       </c>
-      <c r="N19" s="13">
+      <c r="N19" s="12">
         <f>GJ당!F18*(4.1868*10.19)/10^3</f>
         <v>1435.4481724034399</v>
       </c>
-      <c r="O19" s="13">
+      <c r="O19" s="12">
         <f>GJ당!G18*(4.1868*10.19)/10^3</f>
         <v>1051.8282915775198</v>
       </c>
-      <c r="P19" s="13">
+      <c r="P19" s="12">
         <f>GJ당!H18*(4.1868*10.19)/10^3</f>
         <v>976.6411397211599</v>
       </c>
-      <c r="Q19" s="13">
+      <c r="Q19" s="12">
         <f>GJ당!I18*(4.1868*10.19)/10^3</f>
         <v>942.3298795500001</v>
       </c>
-      <c r="R19" s="13">
+      <c r="R19" s="12">
         <f>GJ당!J18*(4.1868*10.19)/10^3</f>
         <v>975.62617524647987</v>
       </c>
-      <c r="S19" s="13">
+      <c r="S19" s="12">
         <f>GJ당!K18*(4.1868*10.19)/10^3</f>
         <v>922.21660288152009</v>
       </c>
-      <c r="T19" s="13">
+      <c r="T19" s="12">
         <f>GJ당!L18*(4.1868*10.19)/10^3</f>
         <v>910.46366410536007</v>
       </c>
-      <c r="U19" s="13">
+      <c r="U19" s="12">
         <f>GJ당!M18*(4.1868*10.19)/10^3</f>
         <v>963.86897012112001</v>
       </c>
-      <c r="V19" s="13">
+      <c r="V19" s="12">
         <f>GJ당!N18*(4.1868*10.19)/10^3</f>
         <v>865.78560201311996</v>
       </c>
-      <c r="W19" s="13">
+      <c r="W19" s="12">
         <f>GJ당!O18*(4.1868*10.19)/10^3</f>
         <v>922.95724110264007</v>
       </c>
     </row>
     <row r="20" spans="10:23" x14ac:dyDescent="0.2">
-      <c r="J20" s="6">
+      <c r="J20" s="13">
         <v>2022</v>
       </c>
       <c r="K20" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="L20" s="7">
+      <c r="L20" s="6">
         <f>GJ당!D19*(4.1868*10.19)/10^3</f>
         <v>900.35753612039991</v>
       </c>
-      <c r="M20" s="7">
+      <c r="M20" s="6">
         <f>GJ당!E19*(4.1868*10.19)/10^3</f>
         <v>1173.24603</v>
       </c>
-      <c r="N20" s="7">
+      <c r="N20" s="6">
         <f>GJ당!F19*(4.1868*10.19)/10^3</f>
         <v>1075.1754609395998</v>
       </c>
-      <c r="O20" s="8">
+      <c r="O20" s="7">
         <f>GJ당!G19*(4.1868*10.19)/10^3</f>
         <v>1148.9760493059598</v>
       </c>
-      <c r="P20" s="8">
+      <c r="P20" s="7">
         <f>GJ당!H19*(4.1868*10.19)/10^3</f>
         <v>794.29524173855975</v>
       </c>
-      <c r="Q20" s="9">
+      <c r="Q20" s="8">
         <f>GJ당!I19*(4.1868*10.19)/10^3</f>
         <v>746.85301199963988</v>
       </c>
-      <c r="R20" s="7">
+      <c r="R20" s="6">
         <f>GJ당!J19*(4.1868*10.19)/10^3</f>
         <v>882.93632579712005</v>
       </c>
-      <c r="S20" s="7">
+      <c r="S20" s="6">
         <f>GJ당!K19*(4.1868*10.19)/10^3</f>
         <v>1250.5829952182401</v>
       </c>
-      <c r="T20" s="7">
+      <c r="T20" s="6">
         <f>GJ당!L19*(4.1868*10.19)/10^3</f>
         <v>1429.2896973332399</v>
       </c>
-      <c r="U20" s="10">
+      <c r="U20" s="9">
         <f>GJ당!M19*(4.1868*10.19)/10^3</f>
         <v>1523.0678924635201</v>
       </c>
-      <c r="V20" s="7">
+      <c r="V20" s="6">
         <f>GJ당!N19*(4.1868*10.19)/10^3</f>
         <v>1485.8896456299601</v>
       </c>
-      <c r="W20" s="7">
+      <c r="W20" s="6">
         <f>GJ당!O19*(4.1868*10.19)/10^3</f>
         <v>1572.2379936284399</v>
       </c>
     </row>
     <row r="21" spans="10:23" x14ac:dyDescent="0.2">
-      <c r="J21" s="6"/>
+      <c r="J21" s="13">
+        <v>2022</v>
+      </c>
       <c r="K21" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="L21" s="10">
+      <c r="L21" s="9">
         <f>GJ당!D20*(4.1868*10.19)/10^3</f>
         <v>75.158993951639999</v>
       </c>
-      <c r="M21" s="10">
+      <c r="M21" s="9">
         <f>GJ당!E20*(4.1868*10.19)/10^3</f>
         <v>75.158993951639999</v>
       </c>
-      <c r="N21" s="10">
+      <c r="N21" s="9">
         <f>GJ당!F20*(4.1868*10.19)/10^3</f>
         <v>75.158993951639999</v>
       </c>
-      <c r="O21" s="10">
+      <c r="O21" s="9">
         <f>GJ당!G20*(4.1868*10.19)/10^3</f>
         <v>75.158993951639999</v>
       </c>
-      <c r="P21" s="11">
+      <c r="P21" s="10">
         <f>GJ당!H20*(4.1868*10.19)/10^3</f>
         <v>44.527459965479999</v>
       </c>
-      <c r="Q21" s="11">
+      <c r="Q21" s="10">
         <f>GJ당!I20*(4.1868*10.19)/10^3</f>
         <v>44.527459965479999</v>
       </c>
-      <c r="R21" s="11">
+      <c r="R21" s="10">
         <f>GJ당!J20*(4.1868*10.19)/10^3</f>
         <v>44.527459965479999</v>
       </c>
-      <c r="S21" s="11">
+      <c r="S21" s="10">
         <f>GJ당!K20*(4.1868*10.19)/10^3</f>
         <v>44.527459965479999</v>
       </c>
-      <c r="T21" s="10">
+      <c r="T21" s="9">
         <f>GJ당!L20*(4.1868*10.19)/10^3</f>
         <v>44.527459965479999</v>
       </c>
-      <c r="U21" s="12">
+      <c r="U21" s="11">
         <f>GJ당!M20*(4.1868*10.19)/10^3</f>
         <v>44.527459965479999</v>
       </c>
-      <c r="V21" s="10">
+      <c r="V21" s="9">
         <f>GJ당!N20*(4.1868*10.19)/10^3</f>
         <v>44.527459965479999</v>
       </c>
-      <c r="W21" s="10">
+      <c r="W21" s="9">
         <f>GJ당!O20*(4.1868*10.19)/10^3</f>
         <v>44.527459965479999</v>
       </c>
     </row>
     <row r="22" spans="10:23" ht="14.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="J22" s="6"/>
+      <c r="J22" s="13">
+        <v>2022</v>
+      </c>
       <c r="K22" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="L22" s="13">
+      <c r="L22" s="12">
         <f>GJ당!D21*(4.1868*10.19)/10^3</f>
         <v>975.51653007204004</v>
       </c>
-      <c r="M22" s="13">
+      <c r="M22" s="12">
         <f>GJ당!E21*(4.1868*10.19)/10^3</f>
         <v>1248.4050239516398</v>
       </c>
-      <c r="N22" s="13">
+      <c r="N22" s="12">
         <f>GJ당!F21*(4.1868*10.19)/10^3</f>
         <v>1150.3344548912401</v>
       </c>
-      <c r="O22" s="13">
+      <c r="O22" s="12">
         <f>GJ당!G21*(4.1868*10.19)/10^3</f>
         <v>1224.1350432575996</v>
       </c>
-      <c r="P22" s="13">
+      <c r="P22" s="12">
         <f>GJ당!H21*(4.1868*10.19)/10^3</f>
         <v>838.82270170403967</v>
       </c>
-      <c r="Q22" s="13">
+      <c r="Q22" s="12">
         <f>GJ당!I21*(4.1868*10.19)/10^3</f>
         <v>791.3804719651198</v>
       </c>
-      <c r="R22" s="13">
+      <c r="R22" s="12">
         <f>GJ당!J21*(4.1868*10.19)/10^3</f>
         <v>927.46378576259985</v>
       </c>
-      <c r="S22" s="13">
+      <c r="S22" s="12">
         <f>GJ당!K21*(4.1868*10.19)/10^3</f>
         <v>1295.11045518372</v>
       </c>
-      <c r="T22" s="13">
+      <c r="T22" s="12">
         <f>GJ당!L21*(4.1868*10.19)/10^3</f>
         <v>1473.8171572987201</v>
       </c>
-      <c r="U22" s="13">
+      <c r="U22" s="12">
         <f>GJ당!M21*(4.1868*10.19)/10^3</f>
         <v>1567.5953524290003</v>
       </c>
-      <c r="V22" s="13">
+      <c r="V22" s="12">
         <f>GJ당!N21*(4.1868*10.19)/10^3</f>
         <v>1530.41710559544</v>
       </c>
-      <c r="W22" s="13">
+      <c r="W22" s="12">
         <f>GJ당!O21*(4.1868*10.19)/10^3</f>
         <v>1616.76545359392</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="J11:J13"/>
-    <mergeCell ref="J14:J16"/>
-    <mergeCell ref="J17:J19"/>
-    <mergeCell ref="J20:J22"/>
-    <mergeCell ref="J8:J10"/>
-  </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -1866,40 +1879,40 @@
       <c r="C16" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="D16" s="7">
+      <c r="D16" s="6">
         <v>35061.07</v>
       </c>
-      <c r="E16" s="7">
+      <c r="E16" s="6">
         <v>34633.22</v>
       </c>
-      <c r="F16" s="7">
+      <c r="F16" s="6">
         <v>32602.13</v>
       </c>
-      <c r="G16" s="8">
+      <c r="G16" s="7">
         <v>23610.37</v>
       </c>
-      <c r="H16" s="8">
+      <c r="H16" s="7">
         <v>21456.799999999999</v>
       </c>
-      <c r="I16" s="9">
+      <c r="I16" s="8">
         <v>20652.570000000003</v>
       </c>
-      <c r="J16" s="7">
+      <c r="J16" s="6">
         <v>21433.01</v>
       </c>
-      <c r="K16" s="7">
+      <c r="K16" s="6">
         <v>20181.13</v>
       </c>
-      <c r="L16" s="7">
+      <c r="L16" s="6">
         <v>19905.650000000001</v>
       </c>
-      <c r="M16" s="10">
+      <c r="M16" s="9">
         <v>21157.43</v>
       </c>
-      <c r="N16" s="7">
+      <c r="N16" s="6">
         <v>18858.43</v>
       </c>
-      <c r="O16" s="7">
+      <c r="O16" s="6">
         <v>20198.490000000002</v>
       </c>
     </row>
@@ -1907,40 +1920,40 @@
       <c r="C17" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D17" s="10">
+      <c r="D17" s="9">
         <v>1043.69</v>
       </c>
-      <c r="E17" s="10">
+      <c r="E17" s="9">
         <v>1043.69</v>
       </c>
-      <c r="F17" s="10">
+      <c r="F17" s="9">
         <v>1043.69</v>
       </c>
-      <c r="G17" s="10">
+      <c r="G17" s="9">
         <v>1043.69</v>
       </c>
-      <c r="H17" s="11">
+      <c r="H17" s="10">
         <v>1434.93</v>
       </c>
-      <c r="I17" s="11">
+      <c r="I17" s="10">
         <v>1434.93</v>
       </c>
-      <c r="J17" s="11">
+      <c r="J17" s="10">
         <v>1434.93</v>
       </c>
-      <c r="K17" s="11">
+      <c r="K17" s="10">
         <v>1434.93</v>
       </c>
-      <c r="L17" s="10">
+      <c r="L17" s="9">
         <v>1434.93</v>
       </c>
-      <c r="M17" s="12">
+      <c r="M17" s="11">
         <v>1434.93</v>
       </c>
-      <c r="N17" s="10">
+      <c r="N17" s="9">
         <v>1434.93</v>
       </c>
-      <c r="O17" s="10">
+      <c r="O17" s="9">
         <v>1434.93</v>
       </c>
     </row>
@@ -1948,51 +1961,51 @@
       <c r="C18" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D18" s="13">
+      <c r="D18" s="12">
         <f>SUM(D16:D17)</f>
         <v>36104.76</v>
       </c>
-      <c r="E18" s="13">
+      <c r="E18" s="12">
         <f t="shared" ref="E18:N18" si="3">SUM(E16:E17)</f>
         <v>35676.910000000003</v>
       </c>
-      <c r="F18" s="13">
+      <c r="F18" s="12">
         <f t="shared" si="3"/>
         <v>33645.82</v>
       </c>
-      <c r="G18" s="13">
+      <c r="G18" s="12">
         <f t="shared" si="3"/>
         <v>24654.059999999998</v>
       </c>
-      <c r="H18" s="13">
+      <c r="H18" s="12">
         <f t="shared" si="3"/>
         <v>22891.73</v>
       </c>
-      <c r="I18" s="13">
+      <c r="I18" s="12">
         <f t="shared" si="3"/>
         <v>22087.500000000004</v>
       </c>
-      <c r="J18" s="13">
+      <c r="J18" s="12">
         <f t="shared" si="3"/>
         <v>22867.94</v>
       </c>
-      <c r="K18" s="13">
+      <c r="K18" s="12">
         <f t="shared" si="3"/>
         <v>21616.06</v>
       </c>
-      <c r="L18" s="13">
+      <c r="L18" s="12">
         <f>SUM(L16:L17)</f>
         <v>21340.58</v>
       </c>
-      <c r="M18" s="13">
+      <c r="M18" s="12">
         <f t="shared" si="3"/>
         <v>22592.36</v>
       </c>
-      <c r="N18" s="13">
+      <c r="N18" s="12">
         <f t="shared" si="3"/>
         <v>20293.36</v>
       </c>
-      <c r="O18" s="13">
+      <c r="O18" s="12">
         <v>21633.420000000002</v>
       </c>
     </row>
@@ -2003,40 +2016,40 @@
       <c r="C19" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="D19" s="7">
+      <c r="D19" s="6">
         <v>21103.7</v>
       </c>
-      <c r="E19" s="7">
+      <c r="E19" s="6">
         <v>27500</v>
       </c>
-      <c r="F19" s="7">
+      <c r="F19" s="6">
         <v>25201.3</v>
       </c>
-      <c r="G19" s="8">
+      <c r="G19" s="7">
         <v>26931.129999999997</v>
       </c>
-      <c r="H19" s="8">
+      <c r="H19" s="7">
         <v>18617.679999999997</v>
       </c>
-      <c r="I19" s="9">
+      <c r="I19" s="8">
         <v>17505.669999999998</v>
       </c>
-      <c r="J19" s="7">
+      <c r="J19" s="6">
         <v>20695.36</v>
       </c>
-      <c r="K19" s="7">
+      <c r="K19" s="6">
         <v>29312.720000000001</v>
       </c>
-      <c r="L19" s="7">
+      <c r="L19" s="6">
         <v>33501.47</v>
       </c>
-      <c r="M19" s="10">
+      <c r="M19" s="9">
         <v>35699.560000000005</v>
       </c>
-      <c r="N19" s="7">
+      <c r="N19" s="6">
         <v>34828.130000000005</v>
       </c>
-      <c r="O19" s="7">
+      <c r="O19" s="6">
         <v>36852.07</v>
       </c>
     </row>
@@ -2044,40 +2057,40 @@
       <c r="C20" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D20" s="10">
+      <c r="D20" s="9">
         <v>1761.67</v>
       </c>
-      <c r="E20" s="10">
+      <c r="E20" s="9">
         <v>1761.67</v>
       </c>
-      <c r="F20" s="10">
+      <c r="F20" s="9">
         <v>1761.67</v>
       </c>
-      <c r="G20" s="10">
+      <c r="G20" s="9">
         <v>1761.67</v>
       </c>
-      <c r="H20" s="11">
+      <c r="H20" s="10">
         <v>1043.69</v>
       </c>
-      <c r="I20" s="11">
+      <c r="I20" s="10">
         <v>1043.69</v>
       </c>
-      <c r="J20" s="11">
+      <c r="J20" s="10">
         <v>1043.69</v>
       </c>
-      <c r="K20" s="11">
+      <c r="K20" s="10">
         <v>1043.69</v>
       </c>
-      <c r="L20" s="10">
+      <c r="L20" s="9">
         <v>1043.69</v>
       </c>
-      <c r="M20" s="12">
+      <c r="M20" s="11">
         <v>1043.69</v>
       </c>
-      <c r="N20" s="10">
+      <c r="N20" s="9">
         <v>1043.69</v>
       </c>
-      <c r="O20" s="10">
+      <c r="O20" s="9">
         <v>1043.69</v>
       </c>
     </row>
@@ -2085,51 +2098,51 @@
       <c r="C21" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D21" s="13">
+      <c r="D21" s="12">
         <f>SUM(D19:D20)</f>
         <v>22865.370000000003</v>
       </c>
-      <c r="E21" s="13">
+      <c r="E21" s="12">
         <f t="shared" ref="E21:O21" si="4">SUM(E19:E20)</f>
         <v>29261.67</v>
       </c>
-      <c r="F21" s="13">
+      <c r="F21" s="12">
         <f t="shared" si="4"/>
         <v>26962.97</v>
       </c>
-      <c r="G21" s="13">
+      <c r="G21" s="12">
         <f t="shared" si="4"/>
         <v>28692.799999999996</v>
       </c>
-      <c r="H21" s="13">
+      <c r="H21" s="12">
         <f t="shared" si="4"/>
         <v>19661.369999999995</v>
       </c>
-      <c r="I21" s="13">
+      <c r="I21" s="12">
         <f t="shared" si="4"/>
         <v>18549.359999999997</v>
       </c>
-      <c r="J21" s="13">
+      <c r="J21" s="12">
         <f t="shared" si="4"/>
         <v>21739.05</v>
       </c>
-      <c r="K21" s="13">
+      <c r="K21" s="12">
         <f t="shared" si="4"/>
         <v>30356.41</v>
       </c>
-      <c r="L21" s="13">
+      <c r="L21" s="12">
         <f t="shared" si="4"/>
         <v>34545.160000000003</v>
       </c>
-      <c r="M21" s="13">
+      <c r="M21" s="12">
         <f t="shared" si="4"/>
         <v>36743.250000000007</v>
       </c>
-      <c r="N21" s="13">
+      <c r="N21" s="12">
         <f t="shared" si="4"/>
         <v>35871.820000000007</v>
       </c>
-      <c r="O21" s="13">
+      <c r="O21" s="12">
         <f t="shared" si="4"/>
         <v>37895.760000000002</v>
       </c>

--- a/5. 월별 적용 LNG 단가_2022년부터.xlsx
+++ b/5. 월별 적용 LNG 단가_2022년부터.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\업무\0. 업무 (2026년)\전력시장 일일실적 분석\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98339662-8CE4-430F-9D1A-3DEC1499D548}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F92E9AE-92C7-417C-9667-9AE00BA2B7A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -623,7 +623,7 @@
       </c>
       <c r="U8" s="3">
         <f>GJ당!M7*(4.1868*10.19)/10^3</f>
-        <v>0</v>
+        <v>980.12504047787991</v>
       </c>
       <c r="V8" s="3">
         <f>GJ당!N7*(4.1868*10.19)/10^3</f>
@@ -679,7 +679,7 @@
       </c>
       <c r="U9" s="3">
         <f>GJ당!M8*(4.1868*10.19)/10^3</f>
-        <v>0</v>
+        <v>90.210673929239988</v>
       </c>
       <c r="V9" s="3">
         <f>GJ당!N8*(4.1868*10.19)/10^3</f>
@@ -735,7 +735,7 @@
       </c>
       <c r="U10" s="4">
         <f>GJ당!M9*(4.1868*10.19)/10^3</f>
-        <v>0</v>
+        <v>1070.3357144071199</v>
       </c>
       <c r="V10" s="4">
         <f>GJ당!N9*(4.1868*10.19)/10^3</f>
@@ -1505,7 +1505,9 @@
       <c r="L7" s="3">
         <v>22692.22</v>
       </c>
-      <c r="M7" s="3"/>
+      <c r="M7" s="3">
+        <v>22973.39</v>
+      </c>
       <c r="N7" s="3"/>
       <c r="O7" s="3"/>
     </row>
@@ -1540,7 +1542,9 @@
       <c r="L8" s="3">
         <v>2114.4699999999998</v>
       </c>
-      <c r="M8" s="3"/>
+      <c r="M8" s="3">
+        <v>2114.4699999999998</v>
+      </c>
       <c r="N8" s="3"/>
       <c r="O8" s="3"/>
     </row>
@@ -1586,7 +1590,7 @@
       </c>
       <c r="M9" s="4">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>25087.86</v>
       </c>
       <c r="N9" s="4">
         <f t="shared" si="0"/>
